--- a/docs/xlsx/jobs-2026-10-03.xlsx
+++ b/docs/xlsx/jobs-2026-10-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,49 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Hospital Outreach Specialist - Boston</t>
+  </si>
+  <si>
+    <t>The Hole in the Wall Gang Fund, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36b97732a165406c927cbe6a2ab85ea7-hospital-outreach-specialist-boston-the-hole-in-the-wall-gang-fund-inc-boston</t>
+  </si>
+  <si>
+    <t>Senior Associate Director of Alumni Relations</t>
+  </si>
+  <si>
+    <t>Teachers College, Columbia University</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/fbf56b35b4db40ab89d7eab53a9edd2f-senior-associate-director-of-alumni-relations-teachers-college-columbia-university-new-york</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +90,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +116,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +594,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-03.xlsx
+++ b/docs/xlsx/jobs-2026-10-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,63 @@
     <t>Link</t>
   </si>
   <si>
+    <t>[UPDATED] Senior Immigration Staff Attorney</t>
+  </si>
+  <si>
+    <t>Her Justice</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdbf5c5c16e6494aac1371b1787c12d7-updated-senior-immigration-staff-attorney-her-justice-new-york</t>
+  </si>
+  <si>
+    <t>Audience Engagement Producer</t>
+  </si>
+  <si>
+    <t>El Tímpano</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5baf23d73dd48b198817b522f1b9712-audience-engagement-producer-el-timpano-oakland</t>
+  </si>
+  <si>
+    <t>Community Builder (Bilingual in English &amp; Chinese)</t>
+  </si>
+  <si>
+    <t>CaringKind, Your Trusted Partner in Alzheimer's and Dementia Care</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1691e77788cf4268b5e1a5d06a099345-community-builder-bilingual-in-english-chinese-caringkind-your-trusted-partner-in-alzheimers-and-dementia-care-new-york</t>
+  </si>
+  <si>
     <t>Hospital Outreach Specialist - Boston</t>
   </si>
   <si>
@@ -49,9 +106,6 @@
     <t>Boston, Massachusetts</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 56000.00 - 59000.00/year</t>
   </si>
   <si>
@@ -61,19 +115,49 @@
     <t>https://www.idealist.org/en/nonprofit-job/36b97732a165406c927cbe6a2ab85ea7-hospital-outreach-specialist-boston-the-hole-in-the-wall-gang-fund-inc-boston</t>
   </si>
   <si>
+    <t>Part-Time (12–20 Hours/Week) Mandarin-Speaking Dementia Specialist/Navigator</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 37.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f4ac1039eca4a0f8e4b0b3a8ef6bc6e-part-time-1220-hoursweek-mandarin-speaking-dementia-specialistnavigator-caringkind-your-trusted-partner-in-alzheimers-and-dementia-care-new-york</t>
+  </si>
+  <si>
     <t>Senior Associate Director of Alumni Relations</t>
   </si>
   <si>
     <t>Teachers College, Columbia University</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>https://www.idealist.org/en/job/fbf56b35b4db40ab89d7eab53a9edd2f-senior-associate-director-of-alumni-relations-teachers-college-columbia-university-new-york</t>
+  </si>
+  <si>
+    <t>Social Media Coordinator</t>
+  </si>
+  <si>
+    <t>The Way Home</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 750.00 - 1000.00/month</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Mental Health, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4aa358454b184683b47d3bc64eb14d44-social-media-coordinator-the-way-home-lexington</t>
   </si>
 </sst>
 </file>
@@ -555,7 +639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -634,10 +718,125 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -645,6 +844,11 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
